--- a/output/NFLX/NFLX.xlsx
+++ b/output/NFLX/NFLX.xlsx
@@ -92,11 +92,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
@@ -120,6 +115,11 @@
         <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -140,29 +140,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -562,7 +562,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$86.00</t>
+          <t>$91.00</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>+9.4%</t>
+          <t>+16.7%</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$85.56</t>
+          <t>$91.22</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>+9.4%</t>
+          <t>+16.7%</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>$91.10</t>
+          <t>$91.25</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>$98.03</t>
+          <t>$103</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Ad-supported tier had 40M+ MAUs growing 34% QoQ as of Q4 2024; the tier represents 35% of new sign-ups and advertising revenue is not yet a disclosed P&amp;L line; monetization gap is multi-year and structurally underpriced at the current multiple.</t>
+          <t>Advertising revenue reached $1.5B+ in FY2025 and brokers model $3.1B in FY2026E (+104% YoY); 60%+ of new sign-ups now choose the ad-supported tier; the monetization ramp is real and the current multiple prices in none of it.</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Operating margin expanded 1,170bps in three years (17.8% in FY2022 to 29.5% in FY2025); content spend growing slower than revenue is the structural driver, and each 100bps of further expansion at current revenue is worth ~$460M pretax.</t>
+          <t>Operating margin expanded 1,170bps in three years (17.8% in FY2022 to 29.5% in FY2025); FCF compounded from $1.6B (FY2022) to $9.5B (FY2025) with management guiding $12.5B for FY2026; each 100bps of further margin expansion at $51B revenue adds ~$510M pretax.</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>At 20x FY2027E EPS of $3.83, the stock is at the cheapest relative multiple in its streaming era, but FY2027 consensus growth of only 6.6% and a 7-month institutional selloff suggest the multiple compression from growth-to-value rerate is not complete.</t>
+          <t>The WBD merger termination fee (~$2.8B gross, received Q1 2026) clears the M&amp;A execution overhang; buybacks resume at $8.8B expected in FY2026; street mean target is $114 vs $78 current, the widest gap in 18 months.</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Valuation method</t>
         </is>
@@ -946,7 +946,7 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>WACC reasoning</t>
         </is>
@@ -959,7 +959,7 @@
     </row>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Terminal growth reasoning</t>
         </is>
@@ -972,7 +972,7 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Cross-check</t>
         </is>
@@ -985,27 +985,27 @@
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Weights reasoning</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Bear 20%: credible but not base case; Netflix has demonstrated durable FCF improvement over four consecutive years, making a complete stall unlikely absent a recession or subscriber shock comparable to Q1 2022. Base 55%: current revenue growth trajectory (15-16%) and margin expansion path are observable and have been consistent; the key uncertainty is the advertising ramp timeline. Bull 15%: requires simultaneous execution across advertising, live events, and international — achievable but requires things going right that are not yet proven at scale. Cross-check 10%: EV/EBITDA anchors the blend to peer multiples; given Netflix's content amortization creates unusual EBITDA optics, this cross-check deserves lower weight than in a traditional industrial DCF. Total: 20% + 55% + 15% + 10% = 100%.</t>
+          <t>Bear 15%: reduced from 20%. The Q1 2026 earnings quality concern (previously cited as a bear pillar) has been resolved: the $2.85B interest income line is the after-tax proceeds of the ~$2.8B gross WBD merger termination fee, not an accounting anomaly. The institutional selling overhang was partly M&amp;A-deal uncertainty; with WBD deal terminated, that technical pressure eases. Bear risk remains on ads ramp and subscriber growth deceleration, but the setup is materially cleaner. Base 55%: unchanged; the 15-16% revenue growth trajectory and FCF improvement from $1.6B (FY2022) to $9.5B (FY2025) are the observable central case. Bull 20%: raised from 15% after broker data confirms ads revenue was $1.5B+ in FY2025 and GS/UBS model $3.1B in FY2026E (+104% YoY). The bull case is no longer speculative; it is increasingly the base scenario for sell-side analysts (GS PT $120, UBS PT $130). Cross-check 10%: EV/EBITDA peer anchoring; Netflix's content amortization creates unusual EBITDA optics, warranting lower cross-check weight. Total: 15% + 55% + 20% + 10% = 100%.</t>
         </is>
       </c>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Data gaps</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Advertising revenue not disclosed separately; Netflix does not report ad tier revenue as a line item. Estimated at sub-$2B annualized based on CPM/MAU math. | Subscriber count no longer disclosed from FY2025 onwards; regional net adds unavailable from public filings. | Exact geographic revenue split (UCAN/EMEA/LATAM/APAC) not available in yfinance; estimated from public disclosures. | Q1 2026 interest income of $2.85B is anomalous and source is unidentified in available data; needs 10-Q verification. | Live events (NFL, WWE) contract economics not publicly disclosed; cost estimates based on public media reporting. | Content obligations off-balance-sheet total as of Q1 2026 not available; FY2024 figure of $22-25B used as approximation. | Gaming MAU and title economics not disclosed. | Adanos sentiment and Twitter/X short-side commentary not available in this session.</t>
+          <t>Advertising revenue confirmed at $1.5B+ in FY2025 (UBS Apr 2026 post-Q1 note) but still not separately disclosed as a P&amp;L line item by Netflix; $3.1B FY2026E estimate per UBS analyst model. | Subscriber count no longer disclosed from FY2025 onwards; regional net adds unavailable from public filings. | Exact geographic revenue split (UCAN/EMEA/LATAM/APAC) not available in yfinance; estimated from public disclosures. | WBD merger termination fee details: exact after-tax cash received and any contingent payment provisions not available in public filings; $2.8B gross per GS/UBS research notes. | Live events (NFL, WWE) contract economics not publicly disclosed; cost estimates based on public media reporting. | Content obligations off-balance-sheet total as of Q1 2026 not available; FY2024 figure of $22-25B used as approximation. | Gaming MAU and title economics not disclosed. | Adanos sentiment and Twitter/X short-side commentary not available in this session.</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
         <v>45.18</v>
       </c>
       <c r="F4" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="5">
@@ -1464,7 +1464,7 @@
         <v>0.158</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.138</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="6">
@@ -1510,7 +1510,7 @@
         <v>30255</v>
       </c>
       <c r="F7" t="n">
-        <v>32000</v>
+        <v>33700</v>
       </c>
     </row>
     <row r="8">
@@ -1532,7 +1532,7 @@
         <v>0.67</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.623</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="9">
@@ -1554,7 +1554,7 @@
         <v>10981</v>
       </c>
       <c r="F9" t="n">
-        <v>15149</v>
+        <v>15435</v>
       </c>
     </row>
     <row r="10">
@@ -1576,7 +1576,7 @@
         <v>9461</v>
       </c>
       <c r="F10" t="n">
-        <v>11350</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="11">
@@ -1598,7 +1598,7 @@
         <v>2.53</v>
       </c>
       <c r="F11" t="n">
-        <v>3.59</v>
+        <v>3.63</v>
       </c>
     </row>
   </sheetData>
@@ -1849,14 +1849,14 @@
         <v>2026</v>
       </c>
       <c r="B16" t="n">
-        <v>11.83</v>
+        <v>12.5</v>
       </c>
       <c r="C16" t="n">
         <v>51.4</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>FY2026E: Revenue at consensus $51.4B. FCF at $11.83B assumes 25% growth from $9.46B base (FY2025), driven by margin expansion from 29.5% to ~31%, ads tier contribution beginning, and operating leverage. Q1 2026 annualized FCF run rate is approximately $20B but that quarter includes an anomalous $2.85B interest income item; $11.83B is a conservative full-year estimate.</t>
+          <t>FY2026E: Revenue at consensus $51.4B. FCF at $12.5B per management guidance (raised post-Q1 2026 from prior $11B; includes after-tax proceeds of approximately $1.5B from the ~$2.8B gross WBD merger termination fee received in Q1 2026). GS estimates $13.0B and UBS estimates $13.1B for FY2026E FCF; $12.5B is the management-guided floor. Operating FCF (ex-termination fee) is approximately $10.5-11B, consistent with 29.5% operating margin expanding to ~31% and beginning ads contribution.</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
           <t>Formula WACC vs band</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>9.50% — within band (8.0%-12.0%)</t>
         </is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11.83</v>
+        <v>12.5</v>
       </c>
       <c r="C20" t="n">
         <v>14.43</v>
@@ -2327,34 +2327,34 @@
           <t>PV (bn)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="n">
-        <v>10.804</v>
-      </c>
-      <c r="C21" s="15" t="n">
+      <c r="B21" s="14" t="n">
+        <v>11.416</v>
+      </c>
+      <c r="C21" s="14" t="n">
         <v>12.035</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="14" t="n">
         <v>13.192</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="14" t="n">
         <v>14.092</v>
       </c>
-      <c r="F21" s="15" t="n">
+      <c r="F21" s="14" t="n">
         <v>14.801</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="14" t="n">
         <v>15.274</v>
       </c>
-      <c r="H21" s="15" t="n">
+      <c r="H21" s="14" t="n">
         <v>15.343</v>
       </c>
-      <c r="I21" s="15" t="n">
+      <c r="I21" s="14" t="n">
         <v>15.134</v>
       </c>
-      <c r="J21" s="15" t="n">
+      <c r="J21" s="14" t="n">
         <v>14.789</v>
       </c>
-      <c r="K21" s="15" t="n">
+      <c r="K21" s="14" t="n">
         <v>14.317</v>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
           <t>Terminal growth rate (g)</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="15" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>139.78</v>
+        <v>140.392</v>
       </c>
     </row>
     <row r="32">
@@ -2431,8 +2431,8 @@
           <t>Implied EV (bn)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n">
-        <v>386.743</v>
+      <c r="B32" s="14" t="n">
+        <v>387.355</v>
       </c>
     </row>
     <row r="33">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>384.643</v>
+        <v>385.255</v>
       </c>
     </row>
     <row r="35">
@@ -2467,13 +2467,13 @@
     </row>
     <row r="36"/>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Implied price per share</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
-        <v>91.09999999999999</v>
+      <c r="B37" s="17" t="n">
+        <v>91.25</v>
       </c>
     </row>
   </sheetData>
@@ -2519,7 +2519,7 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>WACC / Cost of equity</t>
         </is>
@@ -2555,7 +2555,7 @@
           <t>Cost of equity (Ke)</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>0.0450 + 1.200 x 0.0550</t>
         </is>
@@ -2572,7 +2572,7 @@
           <t>Equity weight x Ke</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>0.96 x 0.1110</t>
         </is>
@@ -2589,7 +2589,7 @@
           <t>Debt weight x after-tax Kd</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>0.04 x 0.0290</t>
         </is>
@@ -2606,7 +2606,7 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>0.1066 + 0.0012</t>
         </is>
@@ -2619,7 +2619,7 @@
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>PV of explicit FCF</t>
         </is>
@@ -2676,13 +2676,13 @@
         <v>2026</v>
       </c>
       <c r="B16" t="n">
-        <v>11.83</v>
+        <v>12.5</v>
       </c>
       <c r="C16" t="n">
         <v>0.9132</v>
       </c>
       <c r="D16" t="n">
-        <v>10.804</v>
+        <v>11.416</v>
       </c>
     </row>
     <row r="17">
@@ -2817,15 +2817,15 @@
           <t>Sum (PV explicit FCF)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>139.780B</t>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>140.392B</t>
         </is>
       </c>
     </row>
     <row r="27"/>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Terminal value</t>
         </is>
@@ -2861,7 +2861,7 @@
           <t>Last projected FCF</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>FCF_10</t>
         </is>
@@ -2878,7 +2878,7 @@
           <t>Terminal FCF</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>35.480 x (1 + 0.0350)</t>
         </is>
@@ -2895,7 +2895,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>36.722 / (0.0950 - 0.0350)</t>
         </is>
@@ -2912,7 +2912,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>612.030 / (1+0.0950)^10</t>
         </is>
@@ -2925,7 +2925,7 @@
     </row>
     <row r="35"/>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Bridge to implied price per share</t>
         </is>
@@ -2961,14 +2961,14 @@
           <t>Implied EV</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>139.780 + 246.963</t>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>140.392 + 246.963</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>386.743B</t>
+          <t>387.355B</t>
         </is>
       </c>
     </row>
@@ -2978,14 +2978,14 @@
           <t>Less: net debt</t>
         </is>
       </c>
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>386.743 - 2.100</t>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>387.355 - 2.100</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>384.643B</t>
+          <t>385.255B</t>
         </is>
       </c>
     </row>
@@ -2995,14 +2995,14 @@
           <t>Implied price per share</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
-        <is>
-          <t>384.643B / 4.222B shares</t>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>385.255B / 4.222B shares</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>$91.10</t>
+          <t>$91.25</t>
         </is>
       </c>
     </row>
@@ -3079,113 +3079,113 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>8.50%</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>97.90000000000001</v>
+        <v>98.05</v>
       </c>
       <c r="C4" t="n">
-        <v>104.01</v>
+        <v>104.16</v>
       </c>
       <c r="D4" t="n">
-        <v>111.35</v>
+        <v>111.49</v>
       </c>
       <c r="E4" t="n">
-        <v>120.31</v>
+        <v>120.45</v>
       </c>
       <c r="F4" t="n">
-        <v>131.51</v>
+        <v>131.66</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>9.00%</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>89.47</v>
+        <v>89.62</v>
       </c>
       <c r="C5" t="n">
-        <v>94.43000000000001</v>
+        <v>94.58</v>
       </c>
       <c r="D5" t="n">
-        <v>100.29</v>
+        <v>100.44</v>
       </c>
       <c r="E5" t="n">
-        <v>107.33</v>
+        <v>107.47</v>
       </c>
       <c r="F5" t="n">
-        <v>115.93</v>
+        <v>116.07</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>9.50%</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>82.26000000000001</v>
+        <v>82.41</v>
       </c>
       <c r="C6" t="n">
-        <v>86.34</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>91.09999999999999</v>
+        <v>91.25</v>
       </c>
       <c r="E6" t="n">
-        <v>96.73</v>
+        <v>96.88</v>
       </c>
       <c r="F6" t="n">
-        <v>103.48</v>
+        <v>103.63</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>10.00%</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76.04000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>79.43000000000001</v>
+        <v>79.58</v>
       </c>
       <c r="D7" t="n">
-        <v>83.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>87.92</v>
+        <v>88.06</v>
       </c>
       <c r="F7" t="n">
-        <v>93.31999999999999</v>
+        <v>93.45999999999999</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>10.50%</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70.61</v>
+        <v>70.75</v>
       </c>
       <c r="C8" t="n">
-        <v>73.45999999999999</v>
+        <v>73.61</v>
       </c>
       <c r="D8" t="n">
-        <v>76.72</v>
+        <v>76.86</v>
       </c>
       <c r="E8" t="n">
-        <v>80.48</v>
+        <v>80.62</v>
       </c>
       <c r="F8" t="n">
-        <v>84.87</v>
+        <v>85.01000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3259,24 +3259,24 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="14" t="n">
         <v>20.4</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="14" t="n">
         <v>11.1</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="21" t="n">
         <v>0.162</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="21" t="n">
         <v>-0.139</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="21" t="n">
         <v>-0.356</v>
       </c>
     </row>
@@ -3405,8 +3405,8 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" s="15" t="n">
-        <v>98.03</v>
+      <c r="D14" s="14" t="n">
+        <v>103.27</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
@@ -3498,14 +3498,14 @@
         <v>30.47</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>6.09</v>
+        <v>4.57</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>20% weight. The bear case is credible but not the most likely outcome. Netflix has demonstrated structural FCF improvement over 4 consecutive years ($1.6B to $9.46B), suggesting the business model is durable. However, the Q1 2026 earnings quality issue, seven months of institutional selling, and FY2027 EPS deceleration to 6.6% consensus create a genuine risk that the current multiple reflects growth expectations that will not materialize. The 2022 episode (76% drawdown on a 200K subscriber miss) shows this stock can overshoot to the downside.</t>
+          <t>15% weight, reduced from prior 20%. The bear case loses one key pillar: the Q1 2026 'earnings quality' concern was driven by the ~$2.8B gross WBD merger termination fee received in Q1 2026 (a real cash inflow, not accounting manipulation). Additionally, the 7-month institutional selloff was partly driven by M&amp;A overhang uncertainty from the WBD deal; with the deal terminated and buybacks resuming, that technical pressure is removed. The bear case remains credible on advertising ramp risk and password sharing exhaustion, but the setup is cleaner than it appeared. The 2022 episode (76% drawdown on a subscriber miss) remains the historical tail risk.</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -3515,19 +3515,19 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>91.09999999999999</v>
+        <v>91.25</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0.55</v>
       </c>
       <c r="D6" t="n">
-        <v>50.11</v>
+        <v>50.19</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -3541,23 +3541,23 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>130.43</v>
+        <v>130.64</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>19.56</v>
+        <v>26.13</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>15% weight. The bull case requires the advertising platform to outperform market expectations and Netflix to disclose advertising revenue as a standalone line item, which would force a re-rating. The 40M MAU advertising base growing 34% QoQ supports the trajectory, but achieving $4-5B in advertising revenue by FY2028 requires CPM performance and fill rates that are not yet proven. The live events + gaming + international ARPU combination working simultaneously is a low-probability high-payoff scenario.</t>
+          <t>20% weight, raised from prior 15%. Broker research (GS Apr 2026, UBS Apr 2026) confirms advertising revenue was $1.5B+ in FY2025 (not near-zero as previously modeled) and is tracking to $3.1B in FY2026E (+104% YoY). The advertising thesis is no longer speculative. 60%+ of new sign-ups are now on the ad-supported tier. With the WBD deal terminated and buybacks resuming at $8.8B expected FY2026, capital allocation is clean. GS PT $120, UBS PT $130 both imply the bull case is an achievable central scenario, not a tail. The bull case still requires sequential execution across ads, live events, and international ARPU.</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -3567,19 +3567,19 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98.03</v>
+        <v>103.27</v>
       </c>
       <c r="C8" s="11" t="n">
         <v>0.1</v>
       </c>
       <c r="D8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
@@ -3604,13 +3604,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>BLENDED TARGET</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
-        <v>85.56</v>
+      <c r="D11" s="17" t="n">
+        <v>91.22</v>
       </c>
     </row>
     <row r="12">
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.094</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="14"/>
@@ -3645,7 +3645,7 @@
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Bear 20%: credible but not base case; Netflix has demonstrated durable FCF improvement over four consecutive years, making a complete stall unlikely absent a recession or subscriber shock comparable to Q1 2022. Base 55%: current revenue growth trajectory (15-16%) and margin expansion path are observable and have been consistent; the key uncertainty is the advertising ramp timeline. Bull 15%: requires simultaneous execution across advertising, live events, and international — achievable but requires things going right that are not yet proven at scale. Cross-check 10%: EV/EBITDA anchors the blend to peer multiples; given Netflix's content amortization creates unusual EBITDA optics, this cross-check deserves lower weight than in a traditional industrial DCF. Total: 20% + 55% + 15% + 10% = 100%.</t>
+          <t>Bear 15%: reduced from 20%. The Q1 2026 earnings quality concern (previously cited as a bear pillar) has been resolved: the $2.85B interest income line is the after-tax proceeds of the ~$2.8B gross WBD merger termination fee, not an accounting anomaly. The institutional selling overhang was partly M&amp;A-deal uncertainty; with WBD deal terminated, that technical pressure eases. Bear risk remains on ads ramp and subscriber growth deceleration, but the setup is materially cleaner. Base 55%: unchanged; the 15-16% revenue growth trajectory and FCF improvement from $1.6B (FY2022) to $9.5B (FY2025) are the observable central case. Bull 20%: raised from 15% after broker data confirms ads revenue was $1.5B+ in FY2025 and GS/UBS model $3.1B in FY2026E (+104% YoY). The bull case is no longer speculative; it is increasingly the base scenario for sell-side analysts (GS PT $120, UBS PT $130). Cross-check 10%: EV/EBITDA peer anchoring; Netflix's content amortization creates unusual EBITDA optics, warranting lower cross-check weight. Total: 15% + 55% + 20% + 10% = 100%.</t>
         </is>
       </c>
     </row>
